--- a/sheets/조재수대금교본/검수/토방 마루.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루.xlsx
@@ -4631,11 +4631,7 @@
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="L4" s="21"/>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -4693,28 +4689,18 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">應
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -4727,22 +4713,16 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒣∧
-太
-‹</t>
+          <t xml:space="preserve">㒣
+太</t>
         </is>
       </c>
       <c r="Q6" s="24"/>
@@ -4889,58 +4869,25 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
     <row r="11" ht="91.25" customHeight="true">
@@ -5036,8 +4983,7 @@
       <c r="I12" s="23"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K12" s="23"/>
@@ -5122,29 +5068,25 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -5157,15 +5099,13 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-‹</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O14" s="24"/>
@@ -5179,8 +5119,7 @@
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="S14" s="24"/>
@@ -5196,7 +5135,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞ㄱ
+          <t xml:space="preserve">㳞
 –㴌</t>
         </is>
       </c>
@@ -5324,31 +5263,18 @@
         </is>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-△
-‹</t>
+△</t>
         </is>
       </c>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -5357,11 +5283,7 @@
         </is>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="24"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
@@ -5370,11 +5292,7 @@
         </is>
       </c>
       <c r="Q18" s="24"/>
-      <c r="R18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R18" s="21"/>
       <c r="S18" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/토방 마루.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루.xlsx
@@ -4631,7 +4631,11 @@
         </is>
       </c>
       <c r="K4" s="23"/>
-      <c r="L4" s="21"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="M4" s="23"/>
       <c r="N4" s="21" t="inlineStr">
         <is>
@@ -4721,7 +4725,7 @@
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㒣
+          <t xml:space="preserve">㒣∧
 太</t>
         </is>
       </c>
@@ -5135,7 +5139,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
+          <t xml:space="preserve">㳞ㄱ
 –㴌</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/토방 마루.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루.xlsx
@@ -4485,30 +4485,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="79.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="79.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="79.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="79.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="79.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="79.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="79.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="79.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="79.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="23"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="79.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5068,7 +5068,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="79.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="79.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="79.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="79.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5258,7 +5258,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5305,6 +5305,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>